--- a/model/Outputs/11. Interest rate/20/Output Files/0.3/Output_6_49.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.3/Output_6_49.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3591113.67161436</v>
+        <v>3584246.678665703</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>286.4107162899666</v>
+        <v>286.4107162900007</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>286.4107162899666</v>
+        <v>286.4107162900007</v>
       </c>
     </row>
     <row r="11">
@@ -672,7 +672,7 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H2" t="n">
-        <v>36.71585008894188</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>28.70619138541469</v>
       </c>
       <c r="S2" t="n">
         <v>94.84816780232291</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -751,10 +751,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -790,13 +790,13 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U3" t="n">
-        <v>115.1034760716101</v>
+        <v>4.750944969006421</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
-        <v>385</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X3" t="n">
         <v>19.86273944538755</v>
@@ -845,7 +845,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
-        <v>119.040440756494</v>
+        <v>120.6316114025499</v>
       </c>
       <c r="N4" t="n">
         <v>171.1850752716849</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>326.6021279811511</v>
+        <v>325.0109573350953</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -912,7 +912,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
-        <v>28.70619138541446</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,7 +942,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>94.84816780232291</v>
+        <v>123.5543591877376</v>
       </c>
       <c r="T5" t="n">
         <v>186.6755817285639</v>
@@ -973,16 +973,16 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>170.1516951478433</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>299.8567190531302</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
         <v>147.2737972923793</v>
@@ -1027,7 +1027,7 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2103597601867477</v>
+        <v>385</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>23.54762815777917</v>
+        <v>21.95645751172409</v>
       </c>
       <c r="M7" t="n">
         <v>120.6316114025499</v>
@@ -1097,7 +1097,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>325.0109573350953</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1134,7 +1134,7 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D8" t="n">
-        <v>39.04534712526427</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
         <v>4.363289606868648</v>
@@ -1149,7 +1149,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>28.70619138541446</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1252,28 +1252,28 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>385</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S9" t="n">
-        <v>385</v>
+        <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>133.8419217674477</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
         <v>0.2103597601867477</v>
       </c>
       <c r="V9" t="n">
-        <v>14.51066719152016</v>
+        <v>154.4721739301591</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>385</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>385</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>21.95645751172477</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1334,7 +1334,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>326.6021279811511</v>
+        <v>325.0109573350953</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>384.5565566463266</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C12" t="n">
         <v>11.09991244551929</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R12" t="n">
-        <v>197.2737972923793</v>
+        <v>436.872294727342</v>
       </c>
       <c r="S12" t="n">
         <v>116.5639999646113</v>
@@ -1513,7 +1513,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>112.0691552915768</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1617,7 +1617,7 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H14" t="n">
         <v>58.00965870352741</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>144.8481678023229</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C15" t="n">
         <v>11.09991244551929</v>
@@ -1747,7 +1747,7 @@
         <v>145.050905435271</v>
       </c>
       <c r="X15" t="n">
-        <v>419.8627394453875</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y15" t="n">
         <v>49.39139276613435</v>
@@ -1851,7 +1851,7 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F17" t="n">
-        <v>54.88962870801186</v>
+        <v>58.85502009342638</v>
       </c>
       <c r="G17" t="n">
         <v>53.75737228701621</v>
@@ -1860,7 +1860,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I17" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1921,10 +1921,10 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>75.83998807325922</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D18" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -1981,10 +1981,10 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W18" t="n">
-        <v>82.37314290982852</v>
+        <v>145.050905435271</v>
       </c>
       <c r="X18" t="n">
-        <v>69.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y18" t="n">
         <v>49.39139276613435</v>
@@ -2091,13 +2091,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H20" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I20" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H21" t="n">
-        <v>195.551376634094</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>217.1263858913485</v>
+        <v>86.93822665041519</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2331,7 +2331,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H23" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2382,7 +2382,7 @@
         <v>242.2818334606677</v>
       </c>
       <c r="Y23" t="n">
-        <v>161.3174326828064</v>
+        <v>165.2828240682209</v>
       </c>
     </row>
     <row r="24">
@@ -2398,13 +2398,13 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>239.5984974349628</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>197.2737972923793</v>
@@ -2458,7 +2458,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X24" t="n">
-        <v>69.86273944538755</v>
+        <v>134.6028150731275</v>
       </c>
       <c r="Y24" t="n">
         <v>49.39139276613435</v>
@@ -2553,7 +2553,7 @@
         <v>131.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>99.47457824299391</v>
+        <v>103.4399696284084</v>
       </c>
       <c r="D26" t="n">
         <v>60.33915573984979</v>
@@ -2571,7 +2571,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I26" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2629,13 +2629,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>34.55655664632661</v>
+        <v>99.29663227406654</v>
       </c>
       <c r="C27" t="n">
         <v>11.09991244551929</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -2650,7 +2650,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2686,7 +2686,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U27" t="n">
-        <v>245.7617363942807</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V27" t="n">
         <v>64.51066719152016</v>
@@ -2808,7 +2808,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I29" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S29" t="n">
         <v>144.8481678023229</v>
@@ -2872,10 +2872,10 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>62.67776252544248</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>80.50967533902147</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U30" t="n">
-        <v>400.2103597601867</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V30" t="n">
         <v>64.51066719152016</v>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>131.9993129555745</v>
+        <v>135.964704340989</v>
       </c>
       <c r="C32" t="n">
         <v>99.47457824299391</v>
@@ -3084,7 +3084,7 @@
         <v>299.2212965486107</v>
       </c>
       <c r="V32" t="n">
-        <v>283.8164155522384</v>
+        <v>279.8510241668239</v>
       </c>
       <c r="W32" t="n">
         <v>288.3734759809475</v>
@@ -3106,10 +3106,10 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>86.93822665041522</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -3118,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>259.9515598178218</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S33" t="n">
         <v>116.5639999646113</v>
@@ -3282,7 +3282,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3315,7 +3315,7 @@
         <v>144.8481678023229</v>
       </c>
       <c r="T35" t="n">
-        <v>240.6409731139784</v>
+        <v>236.6755817285639</v>
       </c>
       <c r="U35" t="n">
         <v>299.2212965486107</v>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>62.67776252544243</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3391,13 +3391,13 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S36" t="n">
-        <v>179.2417624900537</v>
+        <v>466.5639999646113</v>
       </c>
       <c r="T36" t="n">
         <v>55.35776521751382</v>
       </c>
       <c r="U36" t="n">
-        <v>400.2103597601867</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V36" t="n">
         <v>64.51066719152016</v>
@@ -3519,7 +3519,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I38" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3564,7 +3564,7 @@
         <v>288.3734759809475</v>
       </c>
       <c r="X38" t="n">
-        <v>242.2818334606677</v>
+        <v>246.2472248460823</v>
       </c>
       <c r="Y38" t="n">
         <v>161.3174326828064</v>
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>62.67776252544243</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>259.9515598178218</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S39" t="n">
         <v>116.5639999646113</v>
@@ -3637,10 +3637,10 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V39" t="n">
-        <v>414.5106671915202</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>82.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X39" t="n">
         <v>69.86273944538755</v>
@@ -3756,7 +3756,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I41" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S41" t="n">
         <v>144.8481678023229</v>
@@ -3814,16 +3814,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>384.5565566463266</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C42" t="n">
         <v>11.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>70.00566530352997</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3877,7 +3877,7 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>145.050905435271</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X42" t="n">
         <v>69.86273944538755</v>
@@ -3990,10 +3990,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H44" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4051,13 +4051,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>34.55655664632661</v>
+        <v>99.29663227406654</v>
       </c>
       <c r="C45" t="n">
         <v>11.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -4108,10 +4108,10 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U45" t="n">
-        <v>400.2103597601867</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V45" t="n">
-        <v>127.1884297169626</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W45" t="n">
         <v>82.37314290982852</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>141.4463380542246</v>
+        <v>112.4501851396645</v>
       </c>
       <c r="C2" t="n">
-        <v>91.47201659665494</v>
+        <v>62.47586368209485</v>
       </c>
       <c r="D2" t="n">
-        <v>81.02842494024101</v>
+        <v>52.03227202568092</v>
       </c>
       <c r="E2" t="n">
-        <v>76.62106170097975</v>
+        <v>47.62490878641967</v>
       </c>
       <c r="F2" t="n">
-        <v>71.68204280399807</v>
+        <v>42.68588988943799</v>
       </c>
       <c r="G2" t="n">
-        <v>67.88671726155745</v>
+        <v>38.89056434699738</v>
       </c>
       <c r="H2" t="n">
         <v>30.8</v>
@@ -4345,28 +4345,28 @@
         <v>1540</v>
       </c>
       <c r="R2" t="n">
-        <v>1540</v>
+        <v>1511.00384708544</v>
       </c>
       <c r="S2" t="n">
-        <v>1444.193769896644</v>
+        <v>1415.197616982083</v>
       </c>
       <c r="T2" t="n">
-        <v>1255.632576231427</v>
+        <v>1226.636423316867</v>
       </c>
       <c r="U2" t="n">
-        <v>1003.893892848992</v>
+        <v>974.8977399344323</v>
       </c>
       <c r="V2" t="n">
-        <v>771.7211411653319</v>
+        <v>742.7249882507717</v>
       </c>
       <c r="W2" t="n">
-        <v>530.9398522956878</v>
+        <v>501.9436993811278</v>
       </c>
       <c r="X2" t="n">
-        <v>336.7157780929932</v>
+        <v>307.7196251784331</v>
       </c>
       <c r="Y2" t="n">
-        <v>224.2739268982392</v>
+        <v>195.2777739836791</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>250.1195817084329</v>
+        <v>717.7755293779028</v>
       </c>
       <c r="C3" t="n">
-        <v>250.1195817084329</v>
+        <v>717.7755293779028</v>
       </c>
       <c r="D3" t="n">
-        <v>250.1195817084329</v>
+        <v>366.3233203903244</v>
       </c>
       <c r="E3" t="n">
-        <v>250.1195817084329</v>
+        <v>366.3233203903244</v>
       </c>
       <c r="F3" t="n">
-        <v>250.1195817084329</v>
+        <v>366.3233203903244</v>
       </c>
       <c r="G3" t="n">
-        <v>250.1195817084329</v>
+        <v>366.3233203903244</v>
       </c>
       <c r="H3" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="I3" t="n">
         <v>30.8</v>
@@ -4433,19 +4433,19 @@
         <v>789.9952208079459</v>
       </c>
       <c r="U3" t="n">
-        <v>673.729083361875</v>
+        <v>785.1962864958182</v>
       </c>
       <c r="V3" t="n">
-        <v>659.071843774481</v>
+        <v>770.5390469084241</v>
       </c>
       <c r="W3" t="n">
-        <v>270.182954885592</v>
+        <v>737.838902555062</v>
       </c>
       <c r="X3" t="n">
-        <v>250.1195817084329</v>
+        <v>717.7755293779028</v>
       </c>
       <c r="Y3" t="n">
-        <v>250.1195817084329</v>
+        <v>717.7755293779028</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>483.736823939226</v>
+        <v>1176.317877464629</v>
       </c>
       <c r="C4" t="n">
-        <v>609.7388297576618</v>
+        <v>1302.319883283064</v>
       </c>
       <c r="D4" t="n">
-        <v>723.0579738826619</v>
+        <v>1415.639027408065</v>
       </c>
       <c r="E4" t="n">
-        <v>723.0579738826619</v>
+        <v>1415.639027408065</v>
       </c>
       <c r="F4" t="n">
-        <v>847.4189464745974</v>
+        <v>1540</v>
       </c>
       <c r="G4" t="n">
-        <v>847.4189464745974</v>
+        <v>1540</v>
       </c>
       <c r="H4" t="n">
-        <v>847.4189464745974</v>
+        <v>1540</v>
       </c>
       <c r="I4" t="n">
-        <v>1068.55182541068</v>
+        <v>1540</v>
       </c>
       <c r="J4" t="n">
-        <v>1429.635566063132</v>
+        <v>1540</v>
       </c>
       <c r="K4" t="n">
         <v>1540</v>
@@ -4488,43 +4488,43 @@
         <v>1516.214517012344</v>
       </c>
       <c r="M4" t="n">
-        <v>1395.97164756134</v>
+        <v>1394.364404484516</v>
       </c>
       <c r="N4" t="n">
-        <v>1223.057430115194</v>
+        <v>1221.450187038369</v>
       </c>
       <c r="O4" t="n">
-        <v>980.1831229646734</v>
+        <v>978.5758798878493</v>
       </c>
       <c r="P4" t="n">
-        <v>689.8317115219688</v>
+        <v>688.2244684451448</v>
       </c>
       <c r="Q4" t="n">
-        <v>360.7011393749001</v>
+        <v>359.0938962980761</v>
       </c>
       <c r="R4" t="n">
         <v>30.8</v>
       </c>
       <c r="S4" t="n">
-        <v>68.05025509417312</v>
+        <v>30.8</v>
       </c>
       <c r="T4" t="n">
-        <v>68.05025509417312</v>
+        <v>184.8569443112008</v>
       </c>
       <c r="U4" t="n">
-        <v>68.05025509417312</v>
+        <v>431.4081369494874</v>
       </c>
       <c r="V4" t="n">
-        <v>68.05025509417312</v>
+        <v>630.2295298354334</v>
       </c>
       <c r="W4" t="n">
-        <v>109.5393945697082</v>
+        <v>802.1204480951108</v>
       </c>
       <c r="X4" t="n">
-        <v>260.5701855939017</v>
+        <v>953.1512391193043</v>
       </c>
       <c r="Y4" t="n">
-        <v>371.9794862729339</v>
+        <v>1064.560539798337</v>
       </c>
     </row>
     <row r="5">
@@ -4534,40 +4534,40 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>141.4463380542246</v>
+        <v>112.4501851396645</v>
       </c>
       <c r="C5" t="n">
-        <v>91.47201659665494</v>
+        <v>62.47586368209485</v>
       </c>
       <c r="D5" t="n">
-        <v>81.02842494024101</v>
+        <v>52.03227202568092</v>
       </c>
       <c r="E5" t="n">
-        <v>76.62106170097975</v>
+        <v>47.62490878641967</v>
       </c>
       <c r="F5" t="n">
-        <v>71.68204280399807</v>
+        <v>42.68588988943799</v>
       </c>
       <c r="G5" t="n">
-        <v>67.88671726155745</v>
+        <v>38.89056434699738</v>
       </c>
       <c r="H5" t="n">
-        <v>59.79615291456007</v>
+        <v>30.8</v>
       </c>
       <c r="I5" t="n">
         <v>30.8</v>
       </c>
       <c r="J5" t="n">
-        <v>396.55</v>
+        <v>411.95</v>
       </c>
       <c r="K5" t="n">
-        <v>396.55</v>
+        <v>793.0999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>396.55</v>
+        <v>793.0999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>777.6999999999999</v>
+        <v>1158.85</v>
       </c>
       <c r="N5" t="n">
         <v>1158.85</v>
@@ -4585,25 +4585,25 @@
         <v>1540</v>
       </c>
       <c r="S5" t="n">
-        <v>1444.193769896644</v>
+        <v>1415.197616982083</v>
       </c>
       <c r="T5" t="n">
-        <v>1255.632576231427</v>
+        <v>1226.636423316867</v>
       </c>
       <c r="U5" t="n">
-        <v>1003.893892848992</v>
+        <v>974.8977399344323</v>
       </c>
       <c r="V5" t="n">
-        <v>771.7211411653319</v>
+        <v>742.7249882507717</v>
       </c>
       <c r="W5" t="n">
-        <v>530.9398522956878</v>
+        <v>501.9436993811278</v>
       </c>
       <c r="X5" t="n">
-        <v>336.7157780929932</v>
+        <v>307.7196251784331</v>
       </c>
       <c r="Y5" t="n">
-        <v>224.2739268982392</v>
+        <v>195.2777739836791</v>
       </c>
     </row>
     <row r="6">
@@ -4613,16 +4613,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>897.189519579215</v>
+        <v>333.6855748011416</v>
       </c>
       <c r="C6" t="n">
-        <v>725.3191204399793</v>
+        <v>333.6855748011416</v>
       </c>
       <c r="D6" t="n">
-        <v>373.8669114524009</v>
+        <v>333.6855748011416</v>
       </c>
       <c r="E6" t="n">
-        <v>373.8669114524009</v>
+        <v>333.6855748011416</v>
       </c>
       <c r="F6" t="n">
         <v>30.8</v>
@@ -4658,31 +4658,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1186.232420368536</v>
+        <v>1011.404879873102</v>
       </c>
       <c r="R6" t="n">
-        <v>1037.471008962092</v>
+        <v>862.6434684666581</v>
       </c>
       <c r="S6" t="n">
-        <v>970.2346453614745</v>
+        <v>795.4071048660406</v>
       </c>
       <c r="T6" t="n">
-        <v>964.8227613033797</v>
+        <v>789.9952208079459</v>
       </c>
       <c r="U6" t="n">
-        <v>964.6102766971304</v>
+        <v>401.106331919057</v>
       </c>
       <c r="V6" t="n">
-        <v>949.9530371097363</v>
+        <v>386.4490923316629</v>
       </c>
       <c r="W6" t="n">
-        <v>917.2528927563742</v>
+        <v>353.7489479783007</v>
       </c>
       <c r="X6" t="n">
-        <v>897.189519579215</v>
+        <v>333.6855748011416</v>
       </c>
       <c r="Y6" t="n">
-        <v>897.189519579215</v>
+        <v>333.6855748011416</v>
       </c>
     </row>
     <row r="7">
@@ -4692,52 +4692,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1244.481409022167</v>
+        <v>539.4261531916877</v>
       </c>
       <c r="C7" t="n">
-        <v>1370.483414840602</v>
+        <v>539.4261531916877</v>
       </c>
       <c r="D7" t="n">
-        <v>1370.483414840602</v>
+        <v>652.7452973166878</v>
       </c>
       <c r="E7" t="n">
-        <v>1370.483414840602</v>
+        <v>770.5742015281008</v>
       </c>
       <c r="F7" t="n">
-        <v>1370.483414840602</v>
+        <v>770.5742015281008</v>
       </c>
       <c r="G7" t="n">
-        <v>1370.483414840602</v>
+        <v>923.9807674149861</v>
       </c>
       <c r="H7" t="n">
-        <v>1540</v>
+        <v>1093.497352574384</v>
       </c>
       <c r="I7" t="n">
-        <v>1540</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="J7" t="n">
         <v>1540</v>
       </c>
       <c r="K7" t="n">
-        <v>1540</v>
+        <v>1540.000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>1516.214517012344</v>
+        <v>1517.821760089168</v>
       </c>
       <c r="M7" t="n">
-        <v>1394.364404484516</v>
+        <v>1395.97164756134</v>
       </c>
       <c r="N7" t="n">
-        <v>1221.450187038369</v>
+        <v>1223.057430115194</v>
       </c>
       <c r="O7" t="n">
-        <v>978.5758798878493</v>
+        <v>980.1831229646734</v>
       </c>
       <c r="P7" t="n">
-        <v>688.2244684451448</v>
+        <v>689.8317115219688</v>
       </c>
       <c r="Q7" t="n">
-        <v>359.0938962980761</v>
+        <v>360.7011393749001</v>
       </c>
       <c r="R7" t="n">
         <v>30.8</v>
@@ -4749,19 +4749,19 @@
         <v>256.125934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>502.6771268912646</v>
+        <v>256.125934252978</v>
       </c>
       <c r="V7" t="n">
-        <v>701.4985197772105</v>
+        <v>256.125934252978</v>
       </c>
       <c r="W7" t="n">
-        <v>873.3894380368879</v>
+        <v>428.0168525126554</v>
       </c>
       <c r="X7" t="n">
-        <v>1021.314770676842</v>
+        <v>428.0168525126554</v>
       </c>
       <c r="Y7" t="n">
-        <v>1132.724071355874</v>
+        <v>539.4261531916877</v>
       </c>
     </row>
     <row r="8">
@@ -4777,43 +4777,43 @@
         <v>91.47201659665494</v>
       </c>
       <c r="D8" t="n">
-        <v>52.03227202568092</v>
+        <v>81.02842494024101</v>
       </c>
       <c r="E8" t="n">
-        <v>47.62490878641967</v>
+        <v>76.62106170097975</v>
       </c>
       <c r="F8" t="n">
-        <v>42.68588988943799</v>
+        <v>71.68204280399807</v>
       </c>
       <c r="G8" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H8" t="n">
-        <v>30.8</v>
+        <v>59.79615291456007</v>
       </c>
       <c r="I8" t="n">
         <v>30.8</v>
       </c>
       <c r="J8" t="n">
-        <v>30.8</v>
+        <v>411.95</v>
       </c>
       <c r="K8" t="n">
-        <v>396.55</v>
+        <v>411.95</v>
       </c>
       <c r="L8" t="n">
-        <v>396.55</v>
+        <v>411.95</v>
       </c>
       <c r="M8" t="n">
-        <v>777.6999999999999</v>
+        <v>793.1</v>
       </c>
       <c r="N8" t="n">
         <v>1158.85</v>
       </c>
       <c r="O8" t="n">
-        <v>1158.85</v>
+        <v>1540</v>
       </c>
       <c r="P8" t="n">
-        <v>1158.85</v>
+        <v>1540</v>
       </c>
       <c r="Q8" t="n">
         <v>1540</v>
@@ -4895,25 +4895,25 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1011.404879873102</v>
+        <v>1186.232420368536</v>
       </c>
       <c r="R9" t="n">
-        <v>622.5159909842129</v>
+        <v>1037.471008962092</v>
       </c>
       <c r="S9" t="n">
-        <v>233.6271020953239</v>
+        <v>970.2346453614745</v>
       </c>
       <c r="T9" t="n">
-        <v>98.43324172416462</v>
+        <v>964.8227613033797</v>
       </c>
       <c r="U9" t="n">
-        <v>98.22075711791538</v>
+        <v>964.6102766971304</v>
       </c>
       <c r="V9" t="n">
-        <v>83.56351753052128</v>
+        <v>808.5777777777778</v>
       </c>
       <c r="W9" t="n">
-        <v>50.86337317715914</v>
+        <v>419.6888888888889</v>
       </c>
       <c r="X9" t="n">
         <v>30.8</v>
@@ -4929,52 +4929,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>625.2013882700658</v>
+        <v>751.2033940885</v>
       </c>
       <c r="C10" t="n">
-        <v>751.2033940885016</v>
+        <v>751.2033940885</v>
       </c>
       <c r="D10" t="n">
-        <v>864.5225382135017</v>
+        <v>864.5225382135001</v>
       </c>
       <c r="E10" t="n">
-        <v>982.3514424249147</v>
+        <v>982.3514424249131</v>
       </c>
       <c r="F10" t="n">
-        <v>1106.71241501685</v>
+        <v>1106.712415016849</v>
       </c>
       <c r="G10" t="n">
-        <v>1260.118980903736</v>
+        <v>1260.118980903734</v>
       </c>
       <c r="H10" t="n">
-        <v>1429.635566063133</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="I10" t="n">
-        <v>1429.635566063133</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="J10" t="n">
-        <v>1429.635566063133</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="K10" t="n">
-        <v>1540.000000000002</v>
+        <v>1540</v>
       </c>
       <c r="L10" t="n">
-        <v>1517.821760089168</v>
+        <v>1516.214517012344</v>
       </c>
       <c r="M10" t="n">
-        <v>1395.97164756134</v>
+        <v>1394.364404484516</v>
       </c>
       <c r="N10" t="n">
-        <v>1223.057430115194</v>
+        <v>1221.450187038369</v>
       </c>
       <c r="O10" t="n">
-        <v>980.1831229646734</v>
+        <v>978.5758798878493</v>
       </c>
       <c r="P10" t="n">
-        <v>689.8317115219688</v>
+        <v>688.2244684451448</v>
       </c>
       <c r="Q10" t="n">
-        <v>360.7011393749001</v>
+        <v>359.0938962980761</v>
       </c>
       <c r="R10" t="n">
         <v>30.8</v>
@@ -4983,22 +4983,22 @@
         <v>68.05025509417312</v>
       </c>
       <c r="T10" t="n">
-        <v>68.05025509417312</v>
+        <v>69.97315450005038</v>
       </c>
       <c r="U10" t="n">
-        <v>314.6014477324597</v>
+        <v>316.524347138337</v>
       </c>
       <c r="V10" t="n">
-        <v>314.6014477324597</v>
+        <v>316.524347138337</v>
       </c>
       <c r="W10" t="n">
-        <v>362.4132595795801</v>
+        <v>488.4152653980144</v>
       </c>
       <c r="X10" t="n">
-        <v>513.4440506037736</v>
+        <v>639.4460564222079</v>
       </c>
       <c r="Y10" t="n">
-        <v>513.4440506037736</v>
+        <v>639.4460564222079</v>
       </c>
     </row>
     <row r="11">
@@ -5032,19 +5032,19 @@
         <v>44.72</v>
       </c>
       <c r="J11" t="n">
-        <v>179.7320762183977</v>
+        <v>179.7320762183976</v>
       </c>
       <c r="K11" t="n">
-        <v>179.7320762183977</v>
+        <v>179.7320762183976</v>
       </c>
       <c r="L11" t="n">
-        <v>179.7320762183977</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M11" t="n">
-        <v>690.5809049473327</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N11" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O11" t="n">
         <v>1797.400904947332</v>
@@ -5132,31 +5132,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>1200.152420368536</v>
+        <v>1025.324879873102</v>
       </c>
       <c r="R12" t="n">
-        <v>1000.885958457041</v>
+        <v>584.0397336838671</v>
       </c>
       <c r="S12" t="n">
-        <v>883.1445443513733</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T12" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U12" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V12" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W12" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X12" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y12" t="n">
-        <v>444.3729990826727</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="13">
@@ -5220,10 +5220,10 @@
         <v>44.72</v>
       </c>
       <c r="T13" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U13" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V13" t="n">
         <v>521.9574820108303</v>
@@ -5245,19 +5245,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C14" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D14" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E14" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F14" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G14" t="n">
         <v>103.3156148520479</v>
@@ -5269,10 +5269,10 @@
         <v>44.72</v>
       </c>
       <c r="J14" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>179.7320762183976</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L14" t="n">
         <v>733.1420762183976</v>
@@ -5293,28 +5293,28 @@
         <v>2236</v>
       </c>
       <c r="R14" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S14" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T14" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U14" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X14" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y14" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="15">
@@ -5390,10 +5390,10 @@
         <v>564.8317184882503</v>
       </c>
       <c r="X15" t="n">
-        <v>140.7279412706871</v>
+        <v>494.2632948060407</v>
       </c>
       <c r="Y15" t="n">
-        <v>90.8376455473191</v>
+        <v>444.3729990826727</v>
       </c>
     </row>
     <row r="16">
@@ -5494,37 +5494,37 @@
         <v>217.0655061454243</v>
       </c>
       <c r="F17" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G17" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H17" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I17" t="n">
         <v>44.72</v>
       </c>
       <c r="J17" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>44.72</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L17" t="n">
-        <v>44.72</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M17" t="n">
-        <v>555.568828728935</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="N17" t="n">
-        <v>1108.978828728935</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="O17" t="n">
-        <v>1662.388828728935</v>
+        <v>2096.259113037656</v>
       </c>
       <c r="P17" t="n">
-        <v>2215.798828728935</v>
+        <v>2096.259113037656</v>
       </c>
       <c r="Q17" t="n">
         <v>2236</v>
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C18" t="n">
-        <v>396.1722089875784</v>
+        <v>44.72</v>
       </c>
       <c r="D18" t="n">
         <v>44.72</v>
@@ -5624,13 +5624,13 @@
         <v>711.3477845844836</v>
       </c>
       <c r="W18" t="n">
-        <v>628.142589726071</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X18" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y18" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="19">
@@ -5734,34 +5734,34 @@
         <v>161.6214367433921</v>
       </c>
       <c r="G20" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H20" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I20" t="n">
         <v>44.72</v>
       </c>
       <c r="J20" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K20" t="n">
-        <v>989.4391130376558</v>
+        <v>598.13</v>
       </c>
       <c r="L20" t="n">
-        <v>989.4391130376558</v>
+        <v>1151.54</v>
       </c>
       <c r="M20" t="n">
-        <v>989.4391130376558</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="N20" t="n">
-        <v>1542.849113037656</v>
+        <v>2215.798828728935</v>
       </c>
       <c r="O20" t="n">
-        <v>1542.849113037656</v>
+        <v>2215.798828728935</v>
       </c>
       <c r="P20" t="n">
-        <v>1797.400904947332</v>
+        <v>2215.798828728935</v>
       </c>
       <c r="Q20" t="n">
         <v>2236</v>
@@ -5813,10 +5813,10 @@
         <v>461.5662247731743</v>
       </c>
       <c r="G21" t="n">
-        <v>461.5662247731743</v>
+        <v>132.5363905559749</v>
       </c>
       <c r="H21" t="n">
-        <v>264.0395817084329</v>
+        <v>132.5363905559749</v>
       </c>
       <c r="I21" t="n">
         <v>44.72</v>
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C23" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D23" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E23" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F23" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G23" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H23" t="n">
         <v>44.72</v>
@@ -5980,22 +5980,22 @@
         <v>44.72</v>
       </c>
       <c r="J23" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K23" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="L23" t="n">
-        <v>436.0291130376557</v>
+        <v>137.1709049473327</v>
       </c>
       <c r="M23" t="n">
-        <v>436.0291130376558</v>
+        <v>137.1709049473327</v>
       </c>
       <c r="N23" t="n">
-        <v>989.4391130376557</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="O23" t="n">
-        <v>1542.849113037656</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P23" t="n">
         <v>1797.400904947332</v>
@@ -6025,7 +6025,7 @@
         <v>729.6854750626902</v>
       </c>
       <c r="Y23" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="24">
@@ -6035,16 +6035,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>297.950717050992</v>
+        <v>407.3842417608302</v>
       </c>
       <c r="C24" t="n">
-        <v>286.7386842777402</v>
+        <v>396.1722089875784</v>
       </c>
       <c r="D24" t="n">
-        <v>286.7386842777402</v>
+        <v>44.72</v>
       </c>
       <c r="E24" t="n">
-        <v>286.7386842777402</v>
+        <v>44.72</v>
       </c>
       <c r="F24" t="n">
         <v>44.72</v>
@@ -6080,31 +6080,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>1025.324879873102</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R24" t="n">
-        <v>826.0584179616072</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S24" t="n">
-        <v>708.3170038559392</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T24" t="n">
-        <v>652.400069292794</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U24" t="n">
-        <v>601.6825341814942</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V24" t="n">
-        <v>536.5202440890496</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W24" t="n">
-        <v>453.3150492306369</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X24" t="n">
-        <v>382.7466255484273</v>
+        <v>492.1801502582655</v>
       </c>
       <c r="Y24" t="n">
-        <v>332.8563298250593</v>
+        <v>442.2898545348975</v>
       </c>
     </row>
     <row r="25">
@@ -6117,19 +6117,19 @@
         <v>877.7566123122328</v>
       </c>
       <c r="C25" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D25" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E25" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F25" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G25" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H25" t="n">
         <v>1377.480007433093</v>
@@ -6196,22 +6196,22 @@
         <v>433.4059340138206</v>
       </c>
       <c r="C26" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D26" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E26" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F26" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G26" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H26" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I26" t="n">
         <v>44.72</v>
@@ -6220,22 +6220,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L26" t="n">
-        <v>436.0291130376557</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M26" t="n">
-        <v>946.8779417665908</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="N26" t="n">
-        <v>1243.990904947333</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="O26" t="n">
-        <v>1797.400904947332</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P26" t="n">
-        <v>1797.400904947332</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="Q26" t="n">
         <v>2236</v>
@@ -6272,25 +6272,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>275.2516144816847</v>
+        <v>407.3842417608302</v>
       </c>
       <c r="C27" t="n">
-        <v>264.0395817084329</v>
+        <v>396.1722089875784</v>
       </c>
       <c r="D27" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="E27" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="F27" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="G27" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="H27" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I27" t="n">
         <v>44.72</v>
@@ -6329,19 +6329,19 @@
         <v>827.2276097882281</v>
       </c>
       <c r="U27" t="n">
-        <v>578.9834316121869</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V27" t="n">
-        <v>513.8211415197422</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W27" t="n">
-        <v>430.6159466613296</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X27" t="n">
-        <v>360.0475229791199</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y27" t="n">
-        <v>310.1572272557519</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="28">
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C28" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D28" t="n">
         <v>1010.366979583462</v>
@@ -6405,22 +6405,22 @@
         <v>44.72</v>
       </c>
       <c r="T28" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U28" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V28" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W28" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X28" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y28" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="29">
@@ -6430,25 +6430,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C29" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D29" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E29" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F29" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G29" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H29" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I29" t="n">
         <v>44.72</v>
@@ -6457,49 +6457,49 @@
         <v>44.72</v>
       </c>
       <c r="K29" t="n">
-        <v>44.72</v>
+        <v>598.13</v>
       </c>
       <c r="L29" t="n">
-        <v>137.1709049473327</v>
+        <v>1151.54</v>
       </c>
       <c r="M29" t="n">
-        <v>137.1709049473327</v>
+        <v>1151.54</v>
       </c>
       <c r="N29" t="n">
-        <v>690.5809049473327</v>
+        <v>1704.95</v>
       </c>
       <c r="O29" t="n">
-        <v>1243.990904947333</v>
+        <v>1704.95</v>
       </c>
       <c r="P29" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q29" t="n">
         <v>2236</v>
       </c>
       <c r="R29" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S29" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T29" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U29" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V29" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W29" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X29" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y29" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="30">
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>119.2429040110725</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C30" t="n">
-        <v>108.0308712378207</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D30" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E30" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="F30" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="G30" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H30" t="n">
         <v>44.72</v>
@@ -6566,19 +6566,19 @@
         <v>827.2276097882281</v>
       </c>
       <c r="U30" t="n">
-        <v>422.9747211415747</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V30" t="n">
-        <v>357.8124310491301</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W30" t="n">
-        <v>274.6072361907175</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X30" t="n">
-        <v>204.0388125085078</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y30" t="n">
-        <v>154.1485167851398</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="31">
@@ -6694,22 +6694,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L32" t="n">
-        <v>436.0291130376557</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M32" t="n">
-        <v>946.8779417665908</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="N32" t="n">
-        <v>1500.287941766591</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="O32" t="n">
-        <v>1500.287941766591</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P32" t="n">
-        <v>1797.400904947332</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="Q32" t="n">
         <v>2236</v>
@@ -6727,16 +6727,16 @@
         <v>1548.378741333841</v>
       </c>
       <c r="V32" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W32" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X32" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y32" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="33">
@@ -6746,19 +6746,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>409.4673863086053</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C33" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D33" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="E33" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="F33" t="n">
-        <v>44.72</v>
+        <v>373.7498342171993</v>
       </c>
       <c r="G33" t="n">
         <v>44.72</v>
@@ -6794,28 +6794,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R33" t="n">
-        <v>937.5750872192206</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S33" t="n">
-        <v>819.8336731135525</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T33" t="n">
-        <v>763.9167385504073</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U33" t="n">
-        <v>713.1992034391076</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V33" t="n">
-        <v>648.0369133466629</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W33" t="n">
-        <v>564.8317184882503</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X33" t="n">
-        <v>494.2632948060406</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y33" t="n">
-        <v>444.3729990826726</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="34">
@@ -6825,16 +6825,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C34" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D34" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E34" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F34" t="n">
         <v>1153.55685638681</v>
@@ -6879,22 +6879,22 @@
         <v>44.72</v>
       </c>
       <c r="T34" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U34" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V34" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W34" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X34" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y34" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="35">
@@ -6904,25 +6904,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C35" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D35" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E35" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F35" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G35" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H35" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I35" t="n">
         <v>44.72</v>
@@ -6931,22 +6931,22 @@
         <v>44.72</v>
       </c>
       <c r="K35" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="L35" t="n">
         <v>598.13</v>
       </c>
-      <c r="L35" t="n">
-        <v>1151.54</v>
-      </c>
       <c r="M35" t="n">
+        <v>1108.978828728935</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1108.978828728935</v>
+      </c>
+      <c r="O35" t="n">
         <v>1662.388828728935</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>2215.798828728935</v>
-      </c>
-      <c r="O35" t="n">
-        <v>2236</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2236</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
@@ -6958,22 +6958,22 @@
         <v>2089.688719391593</v>
       </c>
       <c r="T35" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U35" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V35" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W35" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X35" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y35" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="36">
@@ -6983,25 +6983,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>55.93203277325181</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C36" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="D36" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="E36" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="F36" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="G36" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="H36" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="I36" t="n">
         <v>44.72</v>
@@ -7034,25 +7034,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S36" t="n">
-        <v>819.8336731135527</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T36" t="n">
-        <v>763.9167385504074</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U36" t="n">
-        <v>359.6638499037541</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V36" t="n">
-        <v>294.5015598113094</v>
+        <v>357.8124310491301</v>
       </c>
       <c r="W36" t="n">
-        <v>211.2963649528968</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X36" t="n">
-        <v>140.7279412706871</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y36" t="n">
-        <v>90.8376455473191</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="37">
@@ -7116,10 +7116,10 @@
         <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U37" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V37" t="n">
         <v>521.9574820108303</v>
@@ -7141,46 +7141,46 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C38" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D38" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E38" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F38" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G38" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H38" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I38" t="n">
         <v>44.72</v>
       </c>
       <c r="J38" t="n">
-        <v>179.7320762183974</v>
+        <v>44.72</v>
       </c>
       <c r="K38" t="n">
-        <v>733.1420762183974</v>
+        <v>44.72</v>
       </c>
       <c r="L38" t="n">
-        <v>1286.552076218397</v>
+        <v>137.1709049473327</v>
       </c>
       <c r="M38" t="n">
-        <v>1797.400904947332</v>
+        <v>137.1709049473327</v>
       </c>
       <c r="N38" t="n">
-        <v>1797.400904947332</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="O38" t="n">
-        <v>1797.400904947332</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P38" t="n">
         <v>1797.400904947332</v>
@@ -7207,10 +7207,10 @@
         <v>974.4145997704354</v>
       </c>
       <c r="X38" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y38" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="39">
@@ -7220,13 +7220,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>55.93203277325181</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C39" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="D39" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="E39" t="n">
         <v>44.72</v>
@@ -7268,28 +7268,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R39" t="n">
-        <v>937.5750872192206</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S39" t="n">
-        <v>819.8336731135525</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T39" t="n">
-        <v>763.9167385504073</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U39" t="n">
-        <v>713.1992034391076</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V39" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W39" t="n">
-        <v>211.2963649528968</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X39" t="n">
-        <v>140.7279412706871</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y39" t="n">
-        <v>90.8376455473191</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="40">
@@ -7305,22 +7305,22 @@
         <v>954.2586181306687</v>
       </c>
       <c r="D40" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E40" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F40" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G40" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H40" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I40" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J40" t="n">
         <v>1860.696627021627</v>
@@ -7378,25 +7378,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C41" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D41" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E41" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F41" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G41" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H41" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I41" t="n">
         <v>44.72</v>
@@ -7408,13 +7408,13 @@
         <v>436.0291130376557</v>
       </c>
       <c r="L41" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M41" t="n">
-        <v>1500.287941766591</v>
+        <v>575.7700000000003</v>
       </c>
       <c r="N41" t="n">
-        <v>1682.59</v>
+        <v>1129.18</v>
       </c>
       <c r="O41" t="n">
         <v>1682.59</v>
@@ -7426,28 +7426,28 @@
         <v>2236</v>
       </c>
       <c r="R41" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S41" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T41" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U41" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V41" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W41" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X41" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y41" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="42">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C42" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D42" t="n">
-        <v>44.72</v>
+        <v>390.8534315372855</v>
       </c>
       <c r="E42" t="n">
         <v>44.72</v>
@@ -7520,13 +7520,13 @@
         <v>711.3477845844836</v>
       </c>
       <c r="W42" t="n">
-        <v>564.8317184882503</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X42" t="n">
-        <v>494.2632948060407</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y42" t="n">
-        <v>444.3729990826727</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="43">
@@ -7536,28 +7536,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C43" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D43" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E43" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F43" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G43" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H43" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I43" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J43" t="n">
         <v>1860.696627021627</v>
@@ -7590,22 +7590,22 @@
         <v>44.72</v>
       </c>
       <c r="T43" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U43" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V43" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W43" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X43" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y43" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="44">
@@ -7633,7 +7633,7 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H44" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I44" t="n">
         <v>44.72</v>
@@ -7642,7 +7642,7 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L44" t="n">
         <v>989.4391130376558</v>
@@ -7651,10 +7651,10 @@
         <v>1500.287941766591</v>
       </c>
       <c r="N44" t="n">
-        <v>1682.59</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="O44" t="n">
-        <v>1682.59</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P44" t="n">
         <v>2236</v>
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>55.93203277325181</v>
+        <v>407.3842417608302</v>
       </c>
       <c r="C45" t="n">
-        <v>44.72</v>
+        <v>396.1722089875784</v>
       </c>
       <c r="D45" t="n">
         <v>44.72</v>
@@ -7751,19 +7751,19 @@
         <v>827.2276097882281</v>
       </c>
       <c r="U45" t="n">
-        <v>422.9747211415747</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V45" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W45" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X45" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y45" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="46">
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C46" t="n">
         <v>946.5478354584615</v>
@@ -7827,22 +7827,22 @@
         <v>44.72</v>
       </c>
       <c r="T46" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U46" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V46" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W46" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X46" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y46" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
   </sheetData>
@@ -8201,19 +8201,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>404.4874506895348</v>
+        <v>420.0430062450903</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>384.9999999999999</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>929.2621276423173</v>
+        <v>913.7065720867616</v>
       </c>
       <c r="N5" t="n">
-        <v>862.2489580698352</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O5" t="n">
         <v>70.24786957409245</v>
@@ -8438,10 +8438,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>35.04300624509033</v>
+        <v>420.0430062450903</v>
       </c>
       <c r="K8" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -8450,16 +8450,16 @@
         <v>929.2621276423173</v>
       </c>
       <c r="N8" t="n">
-        <v>862.2489580698352</v>
+        <v>846.6934025142796</v>
       </c>
       <c r="O8" t="n">
-        <v>70.24786957409245</v>
+        <v>455.2478695740924</v>
       </c>
       <c r="P8" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
-        <v>557.8226843274854</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,13 +8675,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>171.4188408091284</v>
+        <v>171.4188408091283</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8690,7 +8690,7 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O11" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
@@ -8912,13 +8912,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>559</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -9149,16 +9149,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N17" t="n">
         <v>1036.248958069835</v>
@@ -9167,10 +9167,10 @@
         <v>629.2478695740924</v>
       </c>
       <c r="P17" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>193.2279078336117</v>
+        <v>313.9750954005603</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,16 +9386,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K20" t="n">
         <v>559</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
         <v>1036.248958069835</v>
@@ -9404,10 +9404,10 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
-        <v>257.410082171668</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>193.2279078336117</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,13 +9623,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>93.38475247205324</v>
       </c>
       <c r="M23" t="n">
         <v>544.2621276423173</v>
@@ -9641,7 +9641,7 @@
         <v>629.2478695740924</v>
       </c>
       <c r="P23" t="n">
-        <v>257.4100821716682</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9863,25 +9863,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>777.3630622928068</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O26" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P26" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>356.9661774925453</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,10 +10100,10 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L29" t="n">
-        <v>93.38475247205324</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M29" t="n">
         <v>544.2621276423173</v>
@@ -10112,13 +10112,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O29" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P29" t="n">
-        <v>559.2870600406815</v>
+        <v>536.7012014548227</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,25 +10337,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M32" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O32" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P32" t="n">
-        <v>300.4011642636528</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>356.9661774925453</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,25 +10574,25 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>559</v>
-      </c>
-      <c r="L35" t="n">
-        <v>559.0000000000001</v>
       </c>
       <c r="M35" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O35" t="n">
-        <v>90.65309308021877</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P35" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q35" t="n">
-        <v>172.8226843274854</v>
+        <v>193.2279078336117</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,25 +10808,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>171.4188408091281</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>559</v>
+        <v>93.38475247205324</v>
       </c>
       <c r="M38" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N38" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O38" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P38" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q38" t="n">
         <v>615.8520732695737</v>
@@ -11051,16 +11051,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1060.271045550332</v>
+        <v>685.4145387153926</v>
       </c>
       <c r="N41" t="n">
-        <v>661.3924512348951</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O41" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P41" t="n">
         <v>559.2870600406815</v>
@@ -11285,22 +11285,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
         <v>559</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>661.3924512348951</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O44" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
-        <v>559.2870600406815</v>
+        <v>184.4305532057413</v>
       </c>
       <c r="Q44" t="n">
         <v>172.8226843274854</v>
@@ -22703,7 +22703,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5911706460559</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.591170646055787</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22937,7 +22937,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.591170646055104</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.591170646055787</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23174,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.591170646054422</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.591170646055787</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -26272,10 +26272,10 @@
         <v>1542690.093990435</v>
       </c>
       <c r="C2" t="n">
+        <v>1542690.093990434</v>
+      </c>
+      <c r="D2" t="n">
         <v>1542690.093990435</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1542690.093990434</v>
       </c>
       <c r="E2" t="n">
         <v>1542736.874407429</v>
@@ -26296,7 +26296,7 @@
         <v>1542736.874407429</v>
       </c>
       <c r="K2" t="n">
-        <v>1542736.874407429</v>
+        <v>1542736.874407428</v>
       </c>
       <c r="L2" t="n">
         <v>1542736.874407429</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995092</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941387</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128454</v>
+        <v>540947.4312259532</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505589</v>
+        <v>535094.4215636665</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983395</v>
+        <v>533137.9258114472</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380802</v>
+        <v>531178.6502511878</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552084</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072473</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495091</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.485398499</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>779220.3690909254</v>
+        <v>777704.51340261</v>
       </c>
       <c r="C6" t="n">
-        <v>916798.3492247401</v>
+        <v>915282.4935364238</v>
       </c>
       <c r="D6" t="n">
-        <v>918859.1211370555</v>
+        <v>917343.2654487401</v>
       </c>
       <c r="E6" t="n">
-        <v>594983.4711808936</v>
+        <v>593241.6213677857</v>
       </c>
       <c r="F6" t="n">
-        <v>938174.3665263978</v>
+        <v>936432.5167132901</v>
       </c>
       <c r="G6" t="n">
-        <v>940119.9429945834</v>
+        <v>938378.0931814756</v>
       </c>
       <c r="H6" t="n">
-        <v>942068.2198118846</v>
+        <v>940326.3699987769</v>
       </c>
       <c r="I6" t="n">
-        <v>944019.2164552453</v>
+        <v>942277.3666421376</v>
       </c>
       <c r="J6" t="n">
-        <v>530452.9526568699</v>
+        <v>528711.102843762</v>
       </c>
       <c r="K6" t="n">
-        <v>947929.4484090894</v>
+        <v>946187.5985959811</v>
       </c>
       <c r="L6" t="n">
-        <v>949888.7239693488</v>
+        <v>948146.874156241</v>
       </c>
       <c r="M6" t="n">
-        <v>890602.7998653281</v>
+        <v>888860.9500522204</v>
       </c>
       <c r="N6" t="n">
-        <v>953815.6969001817</v>
+        <v>952073.8470870741</v>
       </c>
       <c r="O6" t="n">
-        <v>675783.4361579192</v>
+        <v>674041.5863448115</v>
       </c>
       <c r="P6" t="n">
-        <v>957754.0390089295</v>
+        <v>956012.1891958225</v>
       </c>
     </row>
   </sheetData>
@@ -26984,7 +26984,7 @@
         <v>350</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
         <v>-0</v>
@@ -27002,10 +27002,10 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N2" t="n">
         <v>-0</v>
@@ -27033,7 +27033,7 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
@@ -27042,19 +27042,19 @@
         <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
         <v>-0</v>
@@ -27088,7 +27088,7 @@
         <v>174</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G4" t="n">
         <v>-0</v>
@@ -27112,10 +27112,10 @@
         <v>174</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>-0</v>
@@ -27451,7 +27451,7 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="I2" t="n">
         <v>150.0811596826846</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>250.8785988282945</v>
+        <v>222.1724074428797</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27518,7 +27518,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>342.6720972219126</v>
@@ -27530,10 +27530,10 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27569,13 +27569,13 @@
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>285.1068836885766</v>
+        <v>395.4594147911803</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
       </c>
       <c r="W3" t="n">
-        <v>47.37314290982852</v>
+        <v>400</v>
       </c>
       <c r="X3" t="n">
         <v>400</v>
@@ -27612,13 +27612,13 @@
         <v>228.7711261016186</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
-        <v>400</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,19 +27642,19 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
+        <v>362.3734797028554</v>
+      </c>
+      <c r="T4" t="n">
+        <v>365.6376415680767</v>
+      </c>
+      <c r="U4" t="n">
         <v>400</v>
       </c>
-      <c r="T4" t="n">
-        <v>210.0245665062577</v>
-      </c>
-      <c r="U4" t="n">
-        <v>150.9583912744579</v>
-      </c>
       <c r="V4" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W4" t="n">
-        <v>268.2810315311693</v>
+        <v>400</v>
       </c>
       <c r="X4" t="n">
         <v>400</v>
@@ -27691,7 +27691,7 @@
         <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>121.3749682972702</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27721,7 +27721,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>371.2938086145853</v>
       </c>
       <c r="T5" t="n">
         <v>400</v>
@@ -27752,16 +27752,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>190.9482172976759</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>39.77952328474669</v>
       </c>
       <c r="G6" t="n">
         <v>325.7395358750273</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27806,7 +27806,7 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>400</v>
+        <v>15.21035976018675</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
@@ -27828,34 +27828,34 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>287.1138003370787</v>
+      </c>
+      <c r="C7" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D7" t="n">
         <v>400</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>400</v>
-      </c>
-      <c r="D7" t="n">
-        <v>285.5362180555555</v>
-      </c>
-      <c r="E7" t="n">
-        <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
         <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>176.6334556201183</v>
+        <v>262.9151796334162</v>
       </c>
       <c r="J7" t="n">
-        <v>35.26894883590776</v>
+        <v>400</v>
       </c>
       <c r="K7" t="n">
-        <v>288.520773801143</v>
+        <v>288.5207738011439</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27885,16 +27885,16 @@
         <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
         <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>396.8631733492533</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
         <v>400</v>
@@ -27913,7 +27913,7 @@
         <v>400</v>
       </c>
       <c r="D8" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="E8" t="n">
         <v>400</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>121.3749682972702</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -28031,28 +28031,28 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
-        <v>162.2737972923793</v>
+        <v>400</v>
       </c>
       <c r="S9" t="n">
-        <v>81.5639999646113</v>
+        <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>271.5158434500661</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>400</v>
+        <v>260.0384932613611</v>
       </c>
       <c r="W9" t="n">
-        <v>400</v>
+        <v>47.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>34.86273944538755</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28068,7 +28068,7 @@
         <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
         <v>400</v>
@@ -28119,7 +28119,7 @@
         <v>400</v>
       </c>
       <c r="T10" t="n">
-        <v>210.0245665062577</v>
+        <v>211.966889138457</v>
       </c>
       <c r="U10" t="n">
         <v>400</v>
@@ -28128,7 +28128,7 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>274.6675692802454</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
@@ -28223,7 +28223,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="C12" t="n">
         <v>350</v>
@@ -28268,10 +28268,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>350</v>
+        <v>110.4015025650372</v>
       </c>
       <c r="S12" t="n">
         <v>350</v>
@@ -28292,7 +28292,7 @@
         <v>350</v>
       </c>
       <c r="Y12" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13">
@@ -28356,13 +28356,13 @@
         <v>350</v>
       </c>
       <c r="T13" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U13" t="n">
         <v>350</v>
       </c>
       <c r="V13" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="W13" t="n">
         <v>350</v>
@@ -28396,7 +28396,7 @@
         <v>350</v>
       </c>
       <c r="G14" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H14" t="n">
         <v>350</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S14" t="n">
         <v>350</v>
@@ -28460,7 +28460,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>350</v>
@@ -28526,7 +28526,7 @@
         <v>287.3222374745575</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="Y15" t="n">
         <v>350</v>
@@ -28630,7 +28630,7 @@
         <v>350</v>
       </c>
       <c r="F17" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="G17" t="n">
         <v>350</v>
@@ -28639,7 +28639,7 @@
         <v>350</v>
       </c>
       <c r="I17" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28700,10 +28700,10 @@
         <v>350</v>
       </c>
       <c r="C18" t="n">
-        <v>285.2599243722601</v>
+        <v>350</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
         <v>342.6720972219126</v>
@@ -28760,10 +28760,10 @@
         <v>350</v>
       </c>
       <c r="W18" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="X18" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>350</v>
@@ -28870,13 +28870,13 @@
         <v>350</v>
       </c>
       <c r="G20" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H20" t="n">
         <v>350</v>
       </c>
       <c r="I20" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28949,13 +28949,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>136.6167105523271</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>130.1881592409333</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -29110,7 +29110,7 @@
         <v>350</v>
       </c>
       <c r="H23" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I23" t="n">
         <v>150.0811596826846</v>
@@ -29161,7 +29161,7 @@
         <v>350</v>
       </c>
       <c r="Y23" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
     </row>
     <row r="24">
@@ -29177,13 +29177,13 @@
         <v>350</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>100.0377449029141</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>325.7395358750273</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
         <v>350</v>
@@ -29237,7 +29237,7 @@
         <v>350</v>
       </c>
       <c r="X24" t="n">
-        <v>350</v>
+        <v>285.2599243722601</v>
       </c>
       <c r="Y24" t="n">
         <v>350</v>
@@ -29253,7 +29253,7 @@
         <v>350</v>
       </c>
       <c r="C25" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="D25" t="n">
         <v>350</v>
@@ -29268,7 +29268,7 @@
         <v>350</v>
       </c>
       <c r="H25" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="I25" t="n">
         <v>350</v>
@@ -29332,7 +29332,7 @@
         <v>350</v>
       </c>
       <c r="C26" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="D26" t="n">
         <v>350</v>
@@ -29350,7 +29350,7 @@
         <v>350</v>
       </c>
       <c r="I26" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29408,13 +29408,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>350</v>
+        <v>285.2599243722601</v>
       </c>
       <c r="C27" t="n">
         <v>350</v>
       </c>
       <c r="D27" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>342.6720972219126</v>
@@ -29429,7 +29429,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29465,7 +29465,7 @@
         <v>350</v>
       </c>
       <c r="U27" t="n">
-        <v>154.448623365906</v>
+        <v>350</v>
       </c>
       <c r="V27" t="n">
         <v>350</v>
@@ -29493,55 +29493,55 @@
         <v>350</v>
       </c>
       <c r="D28" t="n">
+        <v>350</v>
+      </c>
+      <c r="E28" t="n">
+        <v>350</v>
+      </c>
+      <c r="F28" t="n">
+        <v>350</v>
+      </c>
+      <c r="G28" t="n">
+        <v>350</v>
+      </c>
+      <c r="H28" t="n">
+        <v>350</v>
+      </c>
+      <c r="I28" t="n">
+        <v>350</v>
+      </c>
+      <c r="J28" t="n">
+        <v>350</v>
+      </c>
+      <c r="K28" t="n">
+        <v>350</v>
+      </c>
+      <c r="L28" t="n">
+        <v>350</v>
+      </c>
+      <c r="M28" t="n">
+        <v>350</v>
+      </c>
+      <c r="N28" t="n">
+        <v>350</v>
+      </c>
+      <c r="O28" t="n">
+        <v>350</v>
+      </c>
+      <c r="P28" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>350</v>
+      </c>
+      <c r="R28" t="n">
+        <v>350</v>
+      </c>
+      <c r="S28" t="n">
+        <v>350</v>
+      </c>
+      <c r="T28" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="E28" t="n">
-        <v>350</v>
-      </c>
-      <c r="F28" t="n">
-        <v>350</v>
-      </c>
-      <c r="G28" t="n">
-        <v>350</v>
-      </c>
-      <c r="H28" t="n">
-        <v>350</v>
-      </c>
-      <c r="I28" t="n">
-        <v>350</v>
-      </c>
-      <c r="J28" t="n">
-        <v>350</v>
-      </c>
-      <c r="K28" t="n">
-        <v>350</v>
-      </c>
-      <c r="L28" t="n">
-        <v>350</v>
-      </c>
-      <c r="M28" t="n">
-        <v>350</v>
-      </c>
-      <c r="N28" t="n">
-        <v>350</v>
-      </c>
-      <c r="O28" t="n">
-        <v>350</v>
-      </c>
-      <c r="P28" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>350</v>
-      </c>
-      <c r="R28" t="n">
-        <v>350</v>
-      </c>
-      <c r="S28" t="n">
-        <v>350</v>
-      </c>
-      <c r="T28" t="n">
-        <v>350</v>
       </c>
       <c r="U28" t="n">
         <v>350</v>
@@ -29587,7 +29587,7 @@
         <v>350</v>
       </c>
       <c r="I29" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S29" t="n">
         <v>350</v>
@@ -29651,10 +29651,10 @@
         <v>350</v>
       </c>
       <c r="D30" t="n">
-        <v>285.2599243722602</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>342.6720972219126</v>
+        <v>262.1624218828912</v>
       </c>
       <c r="F30" t="n">
         <v>339.6362423378769</v>
@@ -29663,7 +29663,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H30" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>217.1263858913485</v>
@@ -29702,7 +29702,7 @@
         <v>350</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="V30" t="n">
         <v>350</v>
@@ -29803,7 +29803,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="C32" t="n">
         <v>350</v>
@@ -29863,7 +29863,7 @@
         <v>350</v>
       </c>
       <c r="V32" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="W32" t="n">
         <v>350</v>
@@ -29885,10 +29885,10 @@
         <v>350</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D33" t="n">
-        <v>347.9376868977026</v>
+        <v>260.9994602472874</v>
       </c>
       <c r="E33" t="n">
         <v>342.6720972219126</v>
@@ -29897,7 +29897,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>332.1680871864211</v>
@@ -29930,7 +29930,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R33" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="S33" t="n">
         <v>350</v>
@@ -29973,7 +29973,7 @@
         <v>350</v>
       </c>
       <c r="F34" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="G34" t="n">
         <v>350</v>
@@ -30015,7 +30015,7 @@
         <v>350</v>
       </c>
       <c r="T34" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U34" t="n">
         <v>350</v>
@@ -30061,7 +30061,7 @@
         <v>350</v>
       </c>
       <c r="I35" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30094,7 +30094,7 @@
         <v>350</v>
       </c>
       <c r="T35" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="U35" t="n">
         <v>350</v>
@@ -30140,7 +30140,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I36" t="n">
-        <v>217.1263858913485</v>
+        <v>154.4486233659061</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30170,13 +30170,13 @@
         <v>350</v>
       </c>
       <c r="S36" t="n">
-        <v>287.3222374745576</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
         <v>350</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="V36" t="n">
         <v>350</v>
@@ -30252,13 +30252,13 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
+        <v>350</v>
+      </c>
+      <c r="U37" t="n">
+        <v>350</v>
+      </c>
+      <c r="V37" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="U37" t="n">
-        <v>350</v>
-      </c>
-      <c r="V37" t="n">
-        <v>350</v>
       </c>
       <c r="W37" t="n">
         <v>350</v>
@@ -30298,7 +30298,7 @@
         <v>350</v>
       </c>
       <c r="I38" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30343,7 +30343,7 @@
         <v>350</v>
       </c>
       <c r="X38" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="Y38" t="n">
         <v>350</v>
@@ -30365,7 +30365,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>279.9943346964702</v>
       </c>
       <c r="F39" t="n">
         <v>339.6362423378769</v>
@@ -30404,7 +30404,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="S39" t="n">
         <v>350</v>
@@ -30416,10 +30416,10 @@
         <v>350</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="W39" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>350</v>
@@ -30441,7 +30441,7 @@
         <v>350</v>
       </c>
       <c r="D40" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="E40" t="n">
         <v>350</v>
@@ -30459,7 +30459,7 @@
         <v>350</v>
       </c>
       <c r="J40" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="K40" t="n">
         <v>350</v>
@@ -30535,7 +30535,7 @@
         <v>350</v>
       </c>
       <c r="I41" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S41" t="n">
         <v>350</v>
@@ -30593,16 +30593,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="C42" t="n">
         <v>350</v>
       </c>
       <c r="D42" t="n">
-        <v>347.9376868977026</v>
+        <v>277.9320215941727</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>339.6362423378769</v>
@@ -30656,7 +30656,7 @@
         <v>350</v>
       </c>
       <c r="W42" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="X42" t="n">
         <v>350</v>
@@ -30696,7 +30696,7 @@
         <v>350</v>
       </c>
       <c r="J43" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="K43" t="n">
         <v>350</v>
@@ -30726,7 +30726,7 @@
         <v>350</v>
       </c>
       <c r="T43" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U43" t="n">
         <v>350</v>
@@ -30769,10 +30769,10 @@
         <v>350</v>
       </c>
       <c r="H44" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I44" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30830,13 +30830,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>350</v>
+        <v>285.2599243722601</v>
       </c>
       <c r="C45" t="n">
         <v>350</v>
       </c>
       <c r="D45" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>342.6720972219126</v>
@@ -30887,10 +30887,10 @@
         <v>350</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="V45" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="W45" t="n">
         <v>350</v>
@@ -30912,7 +30912,7 @@
         <v>350</v>
       </c>
       <c r="C46" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="D46" t="n">
         <v>350</v>
@@ -30963,7 +30963,7 @@
         <v>350</v>
       </c>
       <c r="T46" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U46" t="n">
         <v>350</v>
@@ -34898,13 +34898,13 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,19 +34928,19 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>155.613075061819</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>41.90822169245962</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
         <v>152.5563545698924</v>
@@ -34980,19 +34980,19 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>369.4444444444445</v>
+        <v>385</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>384.9999999999999</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>385</v>
+        <v>369.4444444444443</v>
       </c>
       <c r="N5" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -35114,34 +35114,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
         <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>86.28172401329795</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>9.186815169423518e-13</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35171,16 +35171,16 @@
         <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>149.4195279191457</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>112.5346471505376</v>
@@ -35217,10 +35217,10 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="K8" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -35229,16 +35229,16 @@
         <v>385</v>
       </c>
       <c r="N8" t="n">
+        <v>369.4444444444443</v>
+      </c>
+      <c r="O8" t="n">
         <v>385</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35354,7 +35354,7 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>114.4637819444445</v>
@@ -35405,7 +35405,7 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.942322632199252</v>
       </c>
       <c r="U10" t="n">
         <v>249.0416087255421</v>
@@ -35414,7 +35414,7 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>48.2947594415357</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
@@ -35460,7 +35460,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35469,7 +35469,7 @@
         <v>559</v>
       </c>
       <c r="O11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -35642,13 +35642,13 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U13" t="n">
         <v>199.0416087255421</v>
       </c>
       <c r="V13" t="n">
-        <v>143.041020417918</v>
+        <v>150.8296897837838</v>
       </c>
       <c r="W13" t="n">
         <v>123.6271901612903</v>
@@ -35691,13 +35691,13 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>559</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35928,16 +35928,16 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>559</v>
@@ -35946,10 +35946,10 @@
         <v>559</v>
       </c>
       <c r="P17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>20.40522350612631</v>
+        <v>141.1524110730749</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36165,16 +36165,16 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>559</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
         <v>559</v>
@@ -36183,10 +36183,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>257.1230221309866</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>443.0293889420883</v>
+        <v>20.40522350612631</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36402,13 +36402,13 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>93.38475247205324</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -36420,7 +36420,7 @@
         <v>559</v>
       </c>
       <c r="P23" t="n">
-        <v>257.1230221309868</v>
+        <v>559</v>
       </c>
       <c r="Q23" t="n">
         <v>443.0293889420883</v>
@@ -36539,7 +36539,7 @@
         <v>62.88619966292134</v>
       </c>
       <c r="C25" t="n">
-        <v>77.27475335195533</v>
+        <v>69.48608398608951</v>
       </c>
       <c r="D25" t="n">
         <v>64.46378194444452</v>
@@ -36554,7 +36554,7 @@
         <v>104.95612715847</v>
       </c>
       <c r="H25" t="n">
-        <v>113.4402045325156</v>
+        <v>121.2288738983814</v>
       </c>
       <c r="I25" t="n">
         <v>173.3665443798817</v>
@@ -36642,25 +36642,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>300.1141042229716</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>443.0293889420883</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36779,7 +36779,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D28" t="n">
-        <v>56.67511257857869</v>
+        <v>64.46378194444452</v>
       </c>
       <c r="E28" t="n">
         <v>69.01909516304346</v>
@@ -36827,7 +36827,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U28" t="n">
         <v>199.0416087255421</v>
@@ -36879,10 +36879,10 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L29" t="n">
-        <v>93.38475247205324</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -36891,13 +36891,13 @@
         <v>559</v>
       </c>
       <c r="O29" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>559</v>
+        <v>536.4141414141411</v>
       </c>
       <c r="Q29" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37116,25 +37116,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M32" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>300.1141042229714</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>443.0293889420883</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37259,7 +37259,7 @@
         <v>69.01909516304346</v>
       </c>
       <c r="F34" t="n">
-        <v>67.82847466639221</v>
+        <v>75.61714403225807</v>
       </c>
       <c r="G34" t="n">
         <v>104.95612715847</v>
@@ -37301,7 +37301,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U34" t="n">
         <v>199.0416087255421</v>
@@ -37353,25 +37353,25 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>559</v>
-      </c>
-      <c r="L35" t="n">
-        <v>559.0000000000001</v>
       </c>
       <c r="M35" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
         <v>559</v>
       </c>
-      <c r="O35" t="n">
+      <c r="P35" t="n">
+        <v>559</v>
+      </c>
+      <c r="Q35" t="n">
         <v>20.40522350612631</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37538,13 +37538,13 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
       </c>
       <c r="V37" t="n">
-        <v>150.8296897837838</v>
+        <v>143.041020417918</v>
       </c>
       <c r="W37" t="n">
         <v>123.6271901612903</v>
@@ -37587,25 +37587,25 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>136.3758345640378</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>93.38475247205324</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>559</v>
       </c>
-      <c r="L38" t="n">
+      <c r="O38" t="n">
         <v>559</v>
       </c>
-      <c r="M38" t="n">
-        <v>516.0089179080152</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q38" t="n">
         <v>443.0293889420883</v>
@@ -37727,7 +37727,7 @@
         <v>77.27475335195533</v>
       </c>
       <c r="D40" t="n">
-        <v>64.46378194444452</v>
+        <v>56.67511257857869</v>
       </c>
       <c r="E40" t="n">
         <v>69.01909516304346</v>
@@ -37745,7 +37745,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J40" t="n">
-        <v>306.9423817982264</v>
+        <v>314.7310511640923</v>
       </c>
       <c r="K40" t="n">
         <v>61.47922619885696</v>
@@ -37830,16 +37830,16 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>141.1524110730753</v>
+      </c>
+      <c r="N41" t="n">
         <v>559</v>
       </c>
-      <c r="M41" t="n">
-        <v>516.0089179080152</v>
-      </c>
-      <c r="N41" t="n">
-        <v>184.1434931650599</v>
-      </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P41" t="n">
         <v>559</v>
@@ -37982,7 +37982,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J43" t="n">
-        <v>306.9423817982264</v>
+        <v>314.7310511640923</v>
       </c>
       <c r="K43" t="n">
         <v>61.47922619885696</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U43" t="n">
         <v>199.0416087255421</v>
@@ -38064,22 +38064,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
         <v>559</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
+        <v>559</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
         <v>184.1434931650599</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>559</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -38198,7 +38198,7 @@
         <v>62.88619966292134</v>
       </c>
       <c r="C46" t="n">
-        <v>77.27475335195533</v>
+        <v>69.48608398608951</v>
       </c>
       <c r="D46" t="n">
         <v>64.46378194444452</v>
@@ -38249,7 +38249,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U46" t="n">
         <v>199.0416087255421</v>
